--- a/output/第10期計画_地域密着型サービス基準省令の論点整理.xlsx
+++ b/output/第10期計画_地域密着型サービス基準省令の論点整理.xlsx
@@ -1417,7 +1417,7 @@
       <c r="A20" s="7" t="inlineStr">
         <is>
           <t>注）確認事項は業務工程管理表 03_確認事項一覧で一元管理します。計画素案の本文には確認事項の注記を書きません。
-注）「希望時期」のうち令和8年9月26日はサービス見込量 第1次概算の期限によるものです。</t>
+注）「希望時期」のうち令和8年9月26日はサービス見込量の算定の期限によるものです。</t>
         </is>
       </c>
     </row>
